--- a/config/templates/wuping/label_config.xlsx
+++ b/config/templates/wuping/label_config.xlsx
@@ -1212,7 +1212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="12" customWidth="1" style="7" min="1" max="1"/>
@@ -1437,23 +1437,23 @@
           <t>名称区</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>名称最多行数</t>
         </is>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="18" t="n">
+      <c r="D10" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>超出行数时自动截断</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>行</t>
         </is>
@@ -1509,295 +1509,291 @@
           <t>信息字段</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>字段字号</t>
         </is>
       </c>
-      <c r="C13" s="14" t="n">
+      <c r="C13" t="n">
         <v>10</v>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="D13" t="n">
         <v>10</v>
       </c>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>各信息字段（编号/布卡号等）的字体大小</t>
         </is>
       </c>
-      <c r="F13" s="15" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>pt</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customFormat="1" customHeight="1" s="7">
-      <c r="A14" s="16" t="inlineStr">
+    <row r="14" ht="20" customFormat="1" customHeight="1" s="7">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>信息字段</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>备注最多行数</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>备注内容超出行数时自动截断，0 = 不限制</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>行</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customFormat="1" customHeight="1" s="7">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>信息字段</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>标签列宽</t>
         </is>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C15" s="17" t="n">
         <v>58</v>
       </c>
-      <c r="D14" s="18" t="n">
+      <c r="D15" s="18" t="n">
         <v>58</v>
       </c>
-      <c r="E14" s="18" t="inlineStr">
+      <c r="E15" s="18" t="inlineStr">
         <is>
           <t>字段标签文字（如"物料编号"）的列宽</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="F15" s="18" t="inlineStr">
         <is>
           <t>px</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customFormat="1" customHeight="1" s="7">
-      <c r="A15" s="10" t="inlineStr">
+    <row r="16" ht="20" customFormat="1" customHeight="1" s="7">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  【二维码】</t>
         </is>
       </c>
-      <c r="B15" s="19" t="n"/>
-      <c r="C15" s="19" t="n"/>
-      <c r="D15" s="19" t="n"/>
-      <c r="E15" s="19" t="n"/>
-      <c r="F15" s="20" t="n"/>
-    </row>
-    <row r="16" ht="20" customFormat="1" customHeight="1" s="7">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="B16" s="19" t="n"/>
+      <c r="C16" s="19" t="n"/>
+      <c r="D16" s="19" t="n"/>
+      <c r="E16" s="19" t="n"/>
+      <c r="F16" s="20" t="n"/>
+    </row>
+    <row r="17" ht="18" customFormat="1" customHeight="1" s="7">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>二维码</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>显示二维码</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>是 / 否</t>
         </is>
       </c>
-      <c r="F16" s="15" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="18" customFormat="1" customHeight="1" s="7">
-      <c r="A17" s="16" t="inlineStr">
+    <row r="18" ht="18" customFormat="1" customHeight="1" s="7">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>二维码</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>二维码尺寸</t>
         </is>
       </c>
-      <c r="C17" s="17" t="n">
+      <c r="C18" s="17" t="n">
         <v>30</v>
       </c>
-      <c r="D17" s="18" t="n">
+      <c r="D18" s="18" t="n">
         <v>30</v>
       </c>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="E18" s="18" t="inlineStr">
         <is>
           <t>二维码图片边长</t>
         </is>
       </c>
-      <c r="F17" s="18" t="inlineStr">
+      <c r="F18" s="18" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="18" customFormat="1" customHeight="1" s="7">
-      <c r="A18" s="10" t="inlineStr">
+    <row r="19" ht="18" customFormat="1" customHeight="1" s="7">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  【批量打印布局】</t>
         </is>
       </c>
-      <c r="B18" s="19" t="n"/>
-      <c r="C18" s="19" t="n"/>
-      <c r="D18" s="19" t="n"/>
-      <c r="E18" s="19" t="n"/>
-      <c r="F18" s="20" t="n"/>
-    </row>
-    <row r="19" ht="18" customFormat="1" customHeight="1" s="7">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="B19" s="19" t="n"/>
+      <c r="C19" s="19" t="n"/>
+      <c r="D19" s="19" t="n"/>
+      <c r="E19" s="19" t="n"/>
+      <c r="F19" s="20" t="n"/>
+    </row>
+    <row r="20" ht="20" customFormat="1" customHeight="1" s="7">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>批量打印</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>每行标签数</t>
         </is>
       </c>
-      <c r="C19" s="14" t="n">
+      <c r="C20" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="15" t="n">
+      <c r="D20" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="15" t="inlineStr">
+      <c r="E20" s="15" t="inlineStr">
         <is>
           <t>批量打印时每行排列几张标签</t>
         </is>
       </c>
-      <c r="F19" s="15" t="inlineStr">
+      <c r="F20" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="20" customFormat="1" customHeight="1" s="7">
-      <c r="A20" s="16" t="inlineStr">
+    <row r="21" ht="18" customFormat="1" customHeight="1" s="7">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>批量打印</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>标签间距</t>
         </is>
       </c>
-      <c r="C20" s="17" t="n">
+      <c r="C21" t="n">
         <v>4</v>
       </c>
-      <c r="D20" s="18" t="n">
+      <c r="D21" t="n">
         <v>4</v>
       </c>
-      <c r="E20" s="18" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>相邻标签之间的间隙</t>
         </is>
       </c>
-      <c r="F20" s="18" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="18" customFormat="1" customHeight="1" s="7">
-      <c r="A21" s="13" t="inlineStr">
+    <row r="22" ht="18" customFormat="1" customHeight="1" s="7">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>批量打印</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>每页标签数</t>
         </is>
       </c>
-      <c r="C21" s="14" t="n">
+      <c r="C22" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="15" t="n">
+      <c r="D22" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="15" t="inlineStr">
+      <c r="E22" s="15" t="inlineStr">
         <is>
           <t>超过此数量后自动换页（0 = 不限制）</t>
         </is>
       </c>
-      <c r="F21" s="15" t="inlineStr">
+      <c r="F22" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="18" customFormat="1" customHeight="1" s="7">
-      <c r="A22" s="10" t="inlineStr">
+    <row r="23" ht="18" customFormat="1" customHeight="1" s="7">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  【底部信息】</t>
         </is>
       </c>
-      <c r="B22" s="19" t="n"/>
-      <c r="C22" s="19" t="n"/>
-      <c r="D22" s="19" t="n"/>
-      <c r="E22" s="19" t="n"/>
-      <c r="F22" s="20" t="n"/>
-    </row>
-    <row r="23" ht="18" customFormat="1" customHeight="1" s="7">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="B23" s="19" t="n"/>
+      <c r="C23" s="19" t="n"/>
+      <c r="D23" s="19" t="n"/>
+      <c r="E23" s="19" t="n"/>
+      <c r="F23" s="20" t="n"/>
+    </row>
+    <row r="24" customFormat="1" s="7">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>底部信息</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>显示底部信息</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D23" s="15" t="inlineStr">
+      <c r="D24" s="15" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E23" s="15" t="inlineStr">
+      <c r="E24" s="15" t="inlineStr">
         <is>
           <t>是 / 否，控制标签底部打印时间等信息</t>
         </is>
       </c>
-      <c r="F23" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" customFormat="1" s="7">
-      <c r="A24" s="16" t="inlineStr">
-        <is>
-          <t>底部信息</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>底部字体</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>Microsoft YaHei, PingFang SC, Arial, sans-serif</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>Microsoft YaHei, PingFang SC, Arial, sans-serif</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>底部编号与打印时间的字体，多个字体用英文逗号分隔</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
+      <c r="F24" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1811,23 +1807,27 @@
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>底部字号</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="D25" s="18" t="n">
-        <v>7</v>
+          <t>底部字体</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>Microsoft YaHei, PingFang SC, Arial, sans-serif</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>Microsoft YaHei, PingFang SC, Arial, sans-serif</t>
+        </is>
       </c>
       <c r="E25" s="18" t="inlineStr">
         <is>
-          <t>底部编号与打印时间的字体大小</t>
+          <t>底部编号与打印时间的字体，多个字体用英文逗号分隔</t>
         </is>
       </c>
       <c r="F25" s="18" t="inlineStr">
         <is>
-          <t>pt</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1839,57 +1839,85 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
+          <t>底部字号</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="D26" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="E26" s="18" t="inlineStr">
+        <is>
+          <t>底部编号与打印时间的字体大小</t>
+        </is>
+      </c>
+      <c r="F26" s="18" t="inlineStr">
+        <is>
+          <t>pt</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>底部信息</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
           <t>底部左侧内容</t>
         </is>
       </c>
-      <c r="C26" s="17" t="inlineStr">
+      <c r="C27" s="17" t="inlineStr">
         <is>
           <t>吉信德科技</t>
         </is>
       </c>
-      <c r="D26" s="18" t="inlineStr">
+      <c r="D27" s="18" t="inlineStr">
         <is>
           <t>{material_code}</t>
         </is>
       </c>
-      <c r="E26" s="18" t="inlineStr">
+      <c r="E27" s="18" t="inlineStr">
         <is>
           <t>支持占位符：{material_code}、{material_name}、{print_time} 等</t>
         </is>
       </c>
-      <c r="F26" s="18" t="inlineStr">
+      <c r="F27" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>底部信息</t>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>底部右侧内容</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C28" s="14" t="inlineStr">
         <is>
           <t>{print_time}</t>
         </is>
       </c>
-      <c r="D27" s="15" t="inlineStr">
+      <c r="D28" s="15" t="inlineStr">
         <is>
           <t>{print_time}</t>
         </is>
       </c>
-      <c r="E27" s="15" t="inlineStr">
+      <c r="E28" s="15" t="inlineStr">
         <is>
           <t>支持占位符：{material_code}、{material_name}、{print_time} 等</t>
         </is>
       </c>
-      <c r="F27" s="15" t="inlineStr">
+      <c r="F28" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1898,11 +1926,11 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A23:F23"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A20:F20"/>
     <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/templates/wuping/label_config.xlsx
+++ b/config/templates/wuping/label_config.xlsx
@@ -1212,7 +1212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="12" customWidth="1" style="7" min="1" max="1"/>
@@ -1539,293 +1539,289 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
+          <t>字段内容最多行数</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>普通字段内容超出行数时自动截断，0 = 不限制</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>行</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customFormat="1" customHeight="1" s="7">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>信息字段</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
           <t>备注最多行数</t>
         </is>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C15" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D15" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>备注内容超出行数时自动截断，0 = 不限制</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>行</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customFormat="1" customHeight="1" s="7">
-      <c r="A15" s="16" t="inlineStr">
+    <row r="16" ht="20" customFormat="1" customHeight="1" s="7">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>信息字段</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>标签列宽</t>
         </is>
       </c>
-      <c r="C15" s="17" t="n">
+      <c r="C16" s="17" t="n">
         <v>58</v>
       </c>
-      <c r="D15" s="18" t="n">
+      <c r="D16" s="18" t="n">
         <v>58</v>
       </c>
-      <c r="E15" s="18" t="inlineStr">
+      <c r="E16" s="18" t="inlineStr">
         <is>
           <t>字段标签文字（如"物料编号"）的列宽</t>
         </is>
       </c>
-      <c r="F15" s="18" t="inlineStr">
+      <c r="F16" s="18" t="inlineStr">
         <is>
           <t>px</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="20" customFormat="1" customHeight="1" s="7">
-      <c r="A16" s="10" t="inlineStr">
+    <row r="17" ht="18" customFormat="1" customHeight="1" s="7">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  【二维码】</t>
         </is>
       </c>
-      <c r="B16" s="19" t="n"/>
-      <c r="C16" s="19" t="n"/>
-      <c r="D16" s="19" t="n"/>
-      <c r="E16" s="19" t="n"/>
-      <c r="F16" s="20" t="n"/>
-    </row>
-    <row r="17" ht="18" customFormat="1" customHeight="1" s="7">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="B17" s="19" t="n"/>
+      <c r="C17" s="19" t="n"/>
+      <c r="D17" s="19" t="n"/>
+      <c r="E17" s="19" t="n"/>
+      <c r="F17" s="20" t="n"/>
+    </row>
+    <row r="18" ht="18" customFormat="1" customHeight="1" s="7">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>二维码</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>显示二维码</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>是 / 否</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="18" customFormat="1" customHeight="1" s="7">
-      <c r="A18" s="16" t="inlineStr">
+    <row r="19" ht="18" customFormat="1" customHeight="1" s="7">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>二维码</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>二维码尺寸</t>
         </is>
       </c>
-      <c r="C18" s="17" t="n">
+      <c r="C19" s="17" t="n">
         <v>30</v>
       </c>
-      <c r="D18" s="18" t="n">
+      <c r="D19" s="18" t="n">
         <v>30</v>
       </c>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="E19" s="18" t="inlineStr">
         <is>
           <t>二维码图片边长</t>
         </is>
       </c>
-      <c r="F18" s="18" t="inlineStr">
+      <c r="F19" s="18" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="18" customFormat="1" customHeight="1" s="7">
-      <c r="A19" s="10" t="inlineStr">
+    <row r="20" ht="20" customFormat="1" customHeight="1" s="7">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  【批量打印布局】</t>
         </is>
       </c>
-      <c r="B19" s="19" t="n"/>
-      <c r="C19" s="19" t="n"/>
-      <c r="D19" s="19" t="n"/>
-      <c r="E19" s="19" t="n"/>
-      <c r="F19" s="20" t="n"/>
-    </row>
-    <row r="20" ht="20" customFormat="1" customHeight="1" s="7">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="B20" s="19" t="n"/>
+      <c r="C20" s="19" t="n"/>
+      <c r="D20" s="19" t="n"/>
+      <c r="E20" s="19" t="n"/>
+      <c r="F20" s="20" t="n"/>
+    </row>
+    <row r="21" ht="18" customFormat="1" customHeight="1" s="7">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>批量打印</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>每行标签数</t>
         </is>
       </c>
-      <c r="C20" s="14" t="n">
+      <c r="C21" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="15" t="n">
+      <c r="D21" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="E20" s="15" t="inlineStr">
+      <c r="E21" s="15" t="inlineStr">
         <is>
           <t>批量打印时每行排列几张标签</t>
         </is>
       </c>
-      <c r="F20" s="15" t="inlineStr">
+      <c r="F21" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="18" customFormat="1" customHeight="1" s="7">
-      <c r="A21" s="16" t="inlineStr">
+    <row r="22" ht="18" customFormat="1" customHeight="1" s="7">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>批量打印</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>标签间距</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C22" t="n">
         <v>4</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D22" t="n">
         <v>4</v>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>相邻标签之间的间隙</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="18" customFormat="1" customHeight="1" s="7">
-      <c r="A22" s="13" t="inlineStr">
+    <row r="23" ht="18" customFormat="1" customHeight="1" s="7">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>批量打印</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>每页标签数</t>
         </is>
       </c>
-      <c r="C22" s="14" t="n">
+      <c r="C23" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="15" t="n">
+      <c r="D23" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="15" t="inlineStr">
+      <c r="E23" s="15" t="inlineStr">
         <is>
           <t>超过此数量后自动换页（0 = 不限制）</t>
         </is>
       </c>
-      <c r="F22" s="15" t="inlineStr">
+      <c r="F23" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="18" customFormat="1" customHeight="1" s="7">
-      <c r="A23" s="10" t="inlineStr">
+    <row r="24" customFormat="1" s="7">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">  【底部信息】</t>
         </is>
       </c>
-      <c r="B23" s="19" t="n"/>
-      <c r="C23" s="19" t="n"/>
-      <c r="D23" s="19" t="n"/>
-      <c r="E23" s="19" t="n"/>
-      <c r="F23" s="20" t="n"/>
-    </row>
-    <row r="24" customFormat="1" s="7">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="B24" s="19" t="n"/>
+      <c r="C24" s="19" t="n"/>
+      <c r="D24" s="19" t="n"/>
+      <c r="E24" s="19" t="n"/>
+      <c r="F24" s="20" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>底部信息</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B25" s="13" t="inlineStr">
         <is>
           <t>显示底部信息</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D24" s="15" t="inlineStr">
+      <c r="D25" s="15" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E24" s="15" t="inlineStr">
+      <c r="E25" s="15" t="inlineStr">
         <is>
           <t>是 / 否，控制标签底部打印时间等信息</t>
         </is>
       </c>
-      <c r="F24" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>底部信息</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>底部字体</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>Microsoft YaHei, PingFang SC, Arial, sans-serif</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>Microsoft YaHei, PingFang SC, Arial, sans-serif</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>底部编号与打印时间的字体，多个字体用英文逗号分隔</t>
-        </is>
-      </c>
-      <c r="F25" s="18" t="inlineStr">
+      <c r="F25" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1839,23 +1835,27 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>底部字号</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="D26" s="18" t="n">
-        <v>7</v>
+          <t>底部字体</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>Microsoft YaHei, PingFang SC, Arial, sans-serif</t>
+        </is>
+      </c>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>Microsoft YaHei, PingFang SC, Arial, sans-serif</t>
+        </is>
       </c>
       <c r="E26" s="18" t="inlineStr">
         <is>
-          <t>底部编号与打印时间的字体大小</t>
+          <t>底部编号与打印时间的字体，多个字体用英文逗号分隔</t>
         </is>
       </c>
       <c r="F26" s="18" t="inlineStr">
         <is>
-          <t>pt</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1867,57 +1867,85 @@
       </c>
       <c r="B27" s="16" t="inlineStr">
         <is>
+          <t>底部字号</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="D27" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="E27" s="18" t="inlineStr">
+        <is>
+          <t>底部编号与打印时间的字体大小</t>
+        </is>
+      </c>
+      <c r="F27" s="18" t="inlineStr">
+        <is>
+          <t>pt</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>底部信息</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
           <t>底部左侧内容</t>
         </is>
       </c>
-      <c r="C27" s="17" t="inlineStr">
+      <c r="C28" s="17" t="inlineStr">
         <is>
           <t>吉信德科技</t>
         </is>
       </c>
-      <c r="D27" s="18" t="inlineStr">
+      <c r="D28" s="18" t="inlineStr">
         <is>
           <t>{material_code}</t>
         </is>
       </c>
-      <c r="E27" s="18" t="inlineStr">
+      <c r="E28" s="18" t="inlineStr">
         <is>
           <t>支持占位符：{material_code}、{material_name}、{print_time} 等</t>
         </is>
       </c>
-      <c r="F27" s="18" t="inlineStr">
+      <c r="F28" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>底部信息</t>
         </is>
       </c>
-      <c r="B28" s="13" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>底部右侧内容</t>
         </is>
       </c>
-      <c r="C28" s="14" t="inlineStr">
+      <c r="C29" s="14" t="inlineStr">
         <is>
           <t>{print_time}</t>
         </is>
       </c>
-      <c r="D28" s="15" t="inlineStr">
+      <c r="D29" s="15" t="inlineStr">
         <is>
           <t>{print_time}</t>
         </is>
       </c>
-      <c r="E28" s="15" t="inlineStr">
+      <c r="E29" s="15" t="inlineStr">
         <is>
           <t>支持占位符：{material_code}、{material_name}、{print_time} 等</t>
         </is>
       </c>
-      <c r="F28" s="15" t="inlineStr">
+      <c r="F29" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1925,13 +1953,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A3:F3"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A20:F20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
